--- a/Upwork_Templates/1. Employee_Performance_Tracker.xlsx
+++ b/Upwork_Templates/1. Employee_Performance_Tracker.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Upwork_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7238B6F9-3257-4DCF-8D21-3A1D0C361E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1831AC6C-C0A7-4FB2-B05A-69E628E148C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{02059953-C8C0-44BD-9390-221A39ACB78E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="description" sheetId="2" r:id="rId2"/>
+    <sheet name="tracker" sheetId="1" r:id="rId1"/>
+    <sheet name="data" sheetId="3" r:id="rId2"/>
+    <sheet name="questions" sheetId="4" r:id="rId3"/>
+    <sheet name="description" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,9 +39,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve">Employee Performance Tracking </t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Designation</t>
   </si>
 </sst>
 </file>
@@ -115,6 +126,104 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FB187E1-3372-4F1E-BDDD-15EA7D4F3430}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="601980" y="190500"/>
+          <a:ext cx="8641080" cy="2164080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>The METRICS on which employees</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t> would be judged depend on the type of organization. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>However, there must be some UNIVERSAL METRICES that are used in almost all of the organizations.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>First decide the type of organization for which you are going to build the Employee Performance Tracker.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>Then the metrices will be automatically clear.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -593,6 +702,40 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D713C7B-344E-45AA-9822-2918AA05BA22}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F60377A-993E-4FFF-A437-CB67C9C367FA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{581574A3-C18C-4027-91A3-7A9F6491A0C3}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Upwork_Templates/1. Employee_Performance_Tracker.xlsx
+++ b/Upwork_Templates/1. Employee_Performance_Tracker.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Upwork_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1831AC6C-C0A7-4FB2-B05A-69E628E148C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3424ABC1-9372-481F-AAF1-D9D0AC9A4BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{02059953-C8C0-44BD-9390-221A39ACB78E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{02059953-C8C0-44BD-9390-221A39ACB78E}"/>
   </bookViews>
   <sheets>
     <sheet name="tracker" sheetId="1" r:id="rId1"/>
     <sheet name="data" sheetId="3" r:id="rId2"/>
     <sheet name="questions" sheetId="4" r:id="rId3"/>
     <sheet name="description" sheetId="2" r:id="rId4"/>
+    <sheet name="TP_example" sheetId="5" r:id="rId5"/>
+    <sheet name="KPI_Sheet" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t xml:space="preserve">Employee Performance Tracking </t>
   </si>
@@ -50,7 +52,88 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Designation</t>
+    <t>Attendance</t>
+  </si>
+  <si>
+    <t>Task Completion</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>Overall Score</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>GSR</t>
+  </si>
+  <si>
+    <t>TNPS</t>
+  </si>
+  <si>
+    <t>XM</t>
+  </si>
+  <si>
+    <t>AICR</t>
+  </si>
+  <si>
+    <t>Error Rate</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Retail/Consumer Goods</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Consulting</t>
+  </si>
+  <si>
+    <t>Tech/Software/SaaS</t>
+  </si>
+  <si>
+    <t>Construction/Capital Works</t>
+  </si>
+  <si>
+    <t>Logistics/Transportation/Warehousing</t>
+  </si>
+  <si>
+    <t>Financial Services/Banking</t>
+  </si>
+  <si>
+    <t>Hospitality/Food Services</t>
+  </si>
+  <si>
+    <t>Education/Non Profit</t>
+  </si>
+  <si>
+    <t>Universal KPIs</t>
+  </si>
+  <si>
+    <t>Overall Equipment Effectiveness (OEE)</t>
+  </si>
+  <si>
+    <t>Scrap / Defect Rate</t>
+  </si>
+  <si>
+    <t>Machine Downtime</t>
+  </si>
+  <si>
+    <t>Inventory Turnover / Days of Inventory</t>
+  </si>
+  <si>
+    <t>Capacity Utilisation Rate</t>
+  </si>
+  <si>
+    <t>Cycle Time / Lead Time per Product</t>
   </si>
 </sst>
 </file>
@@ -703,13 +786,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D713C7B-344E-45AA-9822-2918AA05BA22}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -718,6 +803,18 @@
       </c>
       <c r="C1" t="s">
         <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -743,4 +840,135 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0148266C-9C36-4D0B-9586-60E9B040B922}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4FB746A-FFDB-4D08-A791-270F7BA233E4}">
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Upwork_Templates/1. Employee_Performance_Tracker.xlsx
+++ b/Upwork_Templates/1. Employee_Performance_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Upwork_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3424ABC1-9372-481F-AAF1-D9D0AC9A4BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FAD55D-94B2-4D86-B5DD-2760FF9750A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{02059953-C8C0-44BD-9390-221A39ACB78E}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="81">
   <si>
     <t xml:space="preserve">Employee Performance Tracking </t>
   </si>
@@ -134,6 +134,156 @@
   </si>
   <si>
     <t>Cycle Time / Lead Time per Product</t>
+  </si>
+  <si>
+    <t>Sales per Square Foot</t>
+  </si>
+  <si>
+    <t>Inventory Turnover Rate</t>
+  </si>
+  <si>
+    <t>Average Transaction Value / Basket Size</t>
+  </si>
+  <si>
+    <t>Customer Conversion Rate</t>
+  </si>
+  <si>
+    <t>Customer Satisfaction / Loyalty Metrics</t>
+  </si>
+  <si>
+    <t>Average Length of Stay (ALOS)</t>
+  </si>
+  <si>
+    <t>Readmission Rate</t>
+  </si>
+  <si>
+    <t>Patient Satisfaction Score</t>
+  </si>
+  <si>
+    <t>Bed Occupancy Rate</t>
+  </si>
+  <si>
+    <t>Operating Margin or Cost per Patient</t>
+  </si>
+  <si>
+    <t>Billable Utilisation Percentage</t>
+  </si>
+  <si>
+    <t>Average Hourly Fee / Rate</t>
+  </si>
+  <si>
+    <t>Project Profit Margin</t>
+  </si>
+  <si>
+    <t>Customer Retention Rate</t>
+  </si>
+  <si>
+    <t>Number of New Service Requests / Conversion Rate</t>
+  </si>
+  <si>
+    <t>Customer Churn Rate</t>
+  </si>
+  <si>
+    <t>Customer Acquisition Cost (CAC)</t>
+  </si>
+  <si>
+    <t>Customer Lifetime Value (CLV or LTV)</t>
+  </si>
+  <si>
+    <t>Monthly Recurring Revenue (MRR) / Annual Recurring Revenue (ARR)</t>
+  </si>
+  <si>
+    <t>Average Revenue per User (ARPU)</t>
+  </si>
+  <si>
+    <t>Budget Variance per Project</t>
+  </si>
+  <si>
+    <t>Time/Days of Project Delay</t>
+  </si>
+  <si>
+    <t>Cost per Square Metre (or Unit)</t>
+  </si>
+  <si>
+    <t>Number of Defects / Rework Rates</t>
+  </si>
+  <si>
+    <t>Resource Utilisation Rate</t>
+  </si>
+  <si>
+    <t>On-Time Delivery Rate</t>
+  </si>
+  <si>
+    <t>Load Utilisation / Load Rate</t>
+  </si>
+  <si>
+    <t>Cost per Delivery Unit / Cost per Mile or Kilometer</t>
+  </si>
+  <si>
+    <t>Inventory Accuracy</t>
+  </si>
+  <si>
+    <t>Freight / Logistics Cost per Unit / Order</t>
+  </si>
+  <si>
+    <t>Assets Under Management (AUM)</t>
+  </si>
+  <si>
+    <t>Loan Loss Ratio / Non-Performing Assets (NPA)</t>
+  </si>
+  <si>
+    <t>Customer Retention / Customer Penetration Rate</t>
+  </si>
+  <si>
+    <t>Capital Adequacy Ratio / Return on Assets (ROA)</t>
+  </si>
+  <si>
+    <t>Revenue per Available Room (RevPAR)</t>
+  </si>
+  <si>
+    <t>Table Turnover Rate</t>
+  </si>
+  <si>
+    <t>Customer Satisfaction / Experience Score</t>
+  </si>
+  <si>
+    <t>Gross Profit on Sales</t>
+  </si>
+  <si>
+    <t>Stock / Inventory Turnover</t>
+  </si>
+  <si>
+    <t>Graduation Rate / Completion Rate</t>
+  </si>
+  <si>
+    <t>Cost per Graduate or Cost per Student</t>
+  </si>
+  <si>
+    <t>Student-Teacher Ratio or Faculty Utilisation</t>
+  </si>
+  <si>
+    <t>Student Satisfaction / Engagement Score</t>
+  </si>
+  <si>
+    <t>Placement Rate (for training institutions)</t>
+  </si>
+  <si>
+    <t>Revenue Growth Rate</t>
+  </si>
+  <si>
+    <t>Profit Margin (Gross, Operating, Net)</t>
+  </si>
+  <si>
+    <t>Customer Satisfaction / Net Promoter Score (NPS)</t>
+  </si>
+  <si>
+    <t>Employee Turnover / Retention Rate</t>
+  </si>
+  <si>
+    <t>Cost per Unit / Cost Efficiency</t>
+  </si>
+  <si>
+    <t>Return on Investment (ROI)</t>
   </si>
 </sst>
 </file>
@@ -891,16 +1041,16 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="41.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -942,30 +1092,180 @@
       <c r="A2" t="s">
         <v>25</v>
       </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>26</v>
       </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" t="s">
+        <v>72</v>
+      </c>
+      <c r="K4" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K5" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
+      </c>
+      <c r="K7" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Upwork_Templates/1. Employee_Performance_Tracker.xlsx
+++ b/Upwork_Templates/1. Employee_Performance_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Upwork_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FAD55D-94B2-4D86-B5DD-2760FF9750A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{015E367A-F773-459B-AE7B-594C1BD48FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{02059953-C8C0-44BD-9390-221A39ACB78E}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="82">
   <si>
     <t xml:space="preserve">Employee Performance Tracking </t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>Return on Investment (ROI)</t>
+  </si>
+  <si>
+    <t>KPIs</t>
   </si>
 </sst>
 </file>
@@ -1037,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4FB746A-FFDB-4D08-A791-270F7BA233E4}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.88671875" bestFit="1" customWidth="1"/>
@@ -1053,7 +1056,7 @@
     <col min="11" max="11" width="41.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1088,7 +1091,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1123,7 +1126,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1158,7 +1161,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1193,7 +1196,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1228,7 +1231,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1260,12 +1263,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
       <c r="K7" t="s">
         <v>80</v>
+      </c>
+      <c r="M7" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
